--- a/SHURUI_Remaining_Translations.xlsx
+++ b/SHURUI_Remaining_Translations.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Instructions for use" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Bold emphasis" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="SEO metadata" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Left out on purpose" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,16 +430,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -449,30 +451,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Where it appears</t>
+          <t>Section on the page</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>What it is</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>English</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
@@ -484,20 +491,25 @@
           <t>About</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>button.label</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Learn more about us</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Amsterdam Office</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Amsterdam Office</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -505,85 +517,106 @@
           <t>About</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>figure_item.value</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Amsterdam Office</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Subheading</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>European business operations and market development.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>About</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Audits and independent assessment</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Body text</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>MDSAP Our Quality Management System has been audited under the Medical Device Single Audit Program.  ISO 26000:2010 BSI Independent Opinion Statement</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>About</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Beijing Manufacturing Facility</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Body text</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Address:
+Bldg 6, No.38, Yongda Road, Daxing District, Beijing</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>About</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Built on proprietary innovation</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Europe  |  United States
 China  |  Canada
 Japan  |  Korea</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>About</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>icon_column.body</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>MDSAP Our Quality Management System has been audited under the Medical Device Si</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>About</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>location_item.body</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>{"type":"doc","content":[{"type":"paragraph","content":[{"text":"Address:","type</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>About</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>location_item.title</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Amsterdam Office</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -591,20 +624,25 @@
           <t>About</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>location_item.subtitle</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>European business operations and market development.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Pioneering a new era of Single-Port surgery</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Button or link label</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Learn more about us</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -612,20 +650,26 @@
           <t>Clinical Applications</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>cta_band.body</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The system is indicated for use in both adult and pediatric patients undergoing </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Pediatric applications</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Body text</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>The system is indicated for use in both adult and pediatric patients undergoing minimally invasive surgical procedures, extending single-port robotic access across a broad range of complex pediatric procedures across urology, general and thoracic surgery.
+For pediatric procedures, the system supports minimally invasive access and controlled surgical maneuverability in small, complex anatomical spaces.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -633,20 +677,25 @@
           <t>Clinical Evidence</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>accordion_item.body</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>{"type":"doc","content":[{"type":"paragraph","content":[{"text":"Upper GI Surger</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Clinical evidence</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Button or link label</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Connect with us</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -654,20 +703,27 @@
           <t>Clinical Evidence</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>accordion_item.body</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>{"type":"doc","content":[{"type":"paragraph","content":[{"text":"Uterine Surgery</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Multi-specialty clinical experience</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Body text</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Clinical experience continues to expand across
+core minimally invasive specialties, reflecting broadening
+procedural diversity and surgical complexity.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -675,20 +731,54 @@
           <t>Clinical Evidence</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>button.label</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Connect with us</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Multi-specialty clinical experience</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Body text</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Upper GI Surgery
+Radical esophagectomy
+Fundoplication for GERD
+Hiatal hernia repair
+Radical gastrectomy (total/proximal/distal)
+Partial gastrectomy for GIST
+Hepatobiliary &amp; Pancreatic (HPB) Surgery
+Hepatectomy
+Pancreaticoduodenectomy
+Distal pancreatectomy with splenectomy
+Roux-en-Y pancreaticojejunostomy reconstruction
+Colorectal Surgery
+Colectomy (total/right/left/transverse/sigmoid)
+Low anterior resection (LAR)
+Intersphincteric resection (ISR)
+Total mesorectal excision (TME)
+Transanal local excision (TAE/TALE)
+Transanal total mesorectal excision (TaTME)
+Rectopexy
+Bariatric Surgery
+Sleeve gastrectomy
+Roux-en-Y gastric bypass
+Hernia Surgery
+TAPP (Transabdominal Preperitoneal Repair)
+TEP (Totally Extraperitoneal Repair)
+Breast Surgery
+Nipple-sparing mastectomy
+Basic Procedures
+Appendectomy
+Cholecystectomy</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -696,46 +786,71 @@
           <t>Clinical Evidence</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>feature_card.title</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Multi-specialty clinical experience</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Body text</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Uterine Surgery
+Total hysterectomy with bilateral salpingo-oophorectomy
+Myomectomy
+Adnexal Surgery
+Adnexectomy
+Ovarian cystectomy
+Pelvic Reconstruction
+Sacrohysteropexy
+Lateral wall suspension
+Gynecologic Oncology
+Radical hysterectomy (early-stage cervical cancer)
+Manipulator-free radical hysterectomy
+Endometrial cancer staging surgery
+vNOTES
+Hysterectomy
+Oophorectomy</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Clinical Evidence</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Safety and feasibility of novel Single-Port Robotic-</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Safety and feasibility of
 novel Single-Port
 Robotic-Assisted
 Lobectomy/
-Segmente</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Clinical Evidence</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>specialty_accordion.body</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Clinical experience continues to expand across
-core minimally invasive specialti</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+Segmentectomy for lung
+cancer</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -743,20 +858,26 @@
           <t>Clinical Library</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>clinical_library.show_filters_label</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Show filters</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Explore clinical experience across surgical specialt</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Body text</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Access a growing collection of surgical videos, clinical cases, and published literature illustrating the application of the SHURUI SP Surgical System across multiple specialties.
+Browse procedural experience, surgical techniques, and peer-reviewed clinical publications by specialty.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -764,20 +885,25 @@
           <t>Clinical Library</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>clinical_library.hide_filters_label</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Hide filters</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Explore clinical experience across surgical specialt</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>sort name</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Sort by</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -785,20 +911,25 @@
           <t>Clinical Library</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>clinical_library.promo_headline</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Interested in learning more?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Explore clinical experience across surgical specialt</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>sort oldest label</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Oldest first</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -806,20 +937,25 @@
           <t>Clinical Library</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>clinical_library.promo_body</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Discover the latest clinical developments, scientific collaborations, product up</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Explore clinical experience across surgical specialt</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Button label</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Show filters</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -827,62 +963,77 @@
           <t>Clinical Library</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>hero_full.body</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Access a growing collection of surgical videos, clinical cases, and published li</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Explore clinical experience across surgical specialt</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Button label</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Hide filters</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>contact_form.success_message</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Thank you. Our team will be in touch shortly.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Clinical Library</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Explore clinical experience across surgical specialt</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Interested in learning more?</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>contact_form.privacy_note</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>{"type":"doc","content":[{"type":"paragraph","content":[{"text":"Your personal d</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Clinical Library</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Explore clinical experience across surgical specialt</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Body text</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Discover the latest clinical developments, scientific collaborations, product updates, and educational activities from SHURUI.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -890,20 +1041,25 @@
           <t>Contact</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>form_field.placeholder</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>John</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Contact Us</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Confirmation message</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Thank you. Our team will be in touch shortly.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -911,20 +1067,26 @@
           <t>Contact</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>form_field.placeholder</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Dough</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Contact Us</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>privacy note</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Your personal data will be processed by Surgerii Robotics to respond to your request.
+For more information about how we process your personal data and your rights, please see our Privacy Policy.</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -932,20 +1094,25 @@
           <t>Contact</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>form_field.placeholder</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Select your country</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Contact Us</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Placeholder text</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -953,20 +1120,25 @@
           <t>Contact</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>form_field.placeholder</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>j.dough@gmail.com</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Contact Us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Placeholder text</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Dough</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -974,20 +1146,25 @@
           <t>Contact</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>form_field.placeholder</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Select an option</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Contact Us</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Placeholder text</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Select your country</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -995,20 +1172,25 @@
           <t>Contact</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>stat.value</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>​</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Contact Us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Placeholder text</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>j.dough@gmail.com</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1016,62 +1198,77 @@
           <t>Contact</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>stat.label</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>CE-Marked for adult &amp; pediatric clinical use</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Contact Us</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Placeholder text</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Select an option</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>showcase_item.watermark</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Console</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Why connect with SHURUI?</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>​</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>showcase_item.body</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Patented continuum-based instruments for precise distal control.</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Why connect with SHURUI?</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Button or link label</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>CE-Marked for adult &amp; pediatric clinical use</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1079,20 +1276,25 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>showcase_item.name</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Patient cart</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Chinese hospitals</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>“The continuous bending capability of the instruments allows precise and stable control in confined anatomical spaces. It provides a level of dexterity that supports delicate dissection around critical structures.”</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1100,20 +1302,25 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>showcase_item.watermark</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Arms</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Chinese hospitals</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Job title</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Thoracic Surgeon – Vithas Madrid Aravaca / Ruber Internacional</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1121,20 +1328,25 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>showcase_item.body</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>For adult and pediatric surgical procedures.</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Instruments</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Body text</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Patented continuum-based instruments for precise distal control.</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1142,20 +1354,25 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>testimonial.quote</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">“The continuous bending capability of the instruments allows precise and stable </t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Patient cart</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Patient cart</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1163,83 +1380,103 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>testimonial.role</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Thoracic Surgeon – Vithas Madrid Aravaca / Ruber Internacional</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Patient cart</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>watermark</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Arms</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Instructions for use</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>ifu_item.title</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>3D Endoscope Reprocessing Instructions</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Patient cart</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Body text</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>For adult and pediatric surgical procedures.</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Instructions for use</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>ifu_item.placeholder</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>(link to PDF see IFU folder)</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SHURUI® Single-Port Surgical Robot</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Shurui</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Instructions for use</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>ifu_item.title</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Accessories Reprocessing Instructions</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Surgeon console</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>watermark</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1247,20 +1484,25 @@
           <t>Instructions for use</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>ifu_item.title</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>3D Endoscope Information</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>3D Endoscope Information</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1268,20 +1510,25 @@
           <t>Instructions for use</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>ifu_item.title</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Energy Instrument Cord Information</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>3D Endoscope Reprocessing Instructions</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>3D Endoscope Reprocessing Instructions</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1289,20 +1536,25 @@
           <t>Instructions for use</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>ifu_item.title</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Instrument Reprocessing Instructions</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>3D Endoscope Reprocessing Instructions</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Placeholder text</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>(link to PDF see IFU folder)</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1310,20 +1562,25 @@
           <t>Instructions for use</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>ifu_item.title</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Instruments Information</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Accessories Reprocessing Instructions</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Accessories Reprocessing Instructions</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1331,20 +1588,25 @@
           <t>Instructions for use</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>ifu_item.title</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Sterile Drape User Manual</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Endoscopic Surgical System Technical Description</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Endoscopic Surgical System Technical Description</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1352,20 +1614,25 @@
           <t>Instructions for use</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>ifu_item.title</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Trocar Incision Protector User Manual</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Endoscopic Surgical System User Manual</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Endoscopic Surgical System User Manual</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1373,20 +1640,25 @@
           <t>Instructions for use</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>ifu_item.title</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Endoscopic Surgical System Technical Description</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Energy Instrument Cord Information</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Energy Instrument Cord Information</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1394,314 +1666,390 @@
           <t>Instructions for use</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>ifu_item.title</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Endoscopic Surgical System User Manual</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Instrument Reprocessing Instructions</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Instrument Reprocessing Instructions</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Instruments Ecosystem</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>grid_card.link_label</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Explore more</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>Instructions for use</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Instruments Information</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Instruments Information</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Instruments Ecosystem</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>media_row.body</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>{"type":"doc","content":[{"type":"paragraph","content":[{"text":"The dual contin</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Instructions for use</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Sterile Drape User Manual</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Sterile Drape User Manual</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SHURUI SP Robot</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>card_grid.headline</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>System composition</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>Instructions for use</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Trocar Incision Protector User Manual</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Trocar Incision Protector User Manual</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SHURUI SP Robot</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>display_heading.line_1</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>System purpose</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>Instruments Ecosystem</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Dual Continuum Mechanism</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Body text</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>The dual continuum nitinol instrument combines a wide range of motion with effective tissue retraction capability. Its total bending range of up to 210°, extensive lateral reach, and short deployment length support access, exposure, and controlled manipulation in anatomically constrained surgical environments.</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SHURUI SP Robot</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>display_heading.line_2</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>intended use</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Instruments Ecosystem</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Maryland bipolar forceps</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Link label</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Explore more</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SHURUI SP Robot</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>statement.body</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>The SHURUI SP Surgical System is a CE-marked robotic platform designed for minim</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>News &amp; events</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>3CVD 2026</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>3CVD 2026</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Search results</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>search_page.title_fallback</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Search</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>News &amp; events</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>ERUS 2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>ERUS 2026</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Search results</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>search_page.placeholder</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Search input</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>News &amp; events</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Interested in learning more?</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Interested in learning more?</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Search results</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>search_page.field_label</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Search this site</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>News &amp; events</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Interested in learning more?</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Body text</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Discover the latest clinical developments, scientific collaborations, product updates, and educational activities from SHURUI.</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Search results</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>search_page.sort_name</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Sort by</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>SHURUI SP Robot</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Single-Port Surgical System</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Body text</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>The SHURUI SP Surgical System is a CE-marked robotic platform designed for minimally invasive surgery through a single access point. Its patented Dual Continuum Mechanism enables continuous bending of robotic instruments, supporting versatile control and access within complex anatomical spaces.
+The SHURUI® Endoscopic Surgical System is intended to assist in the accurate control of the SHURUI® instruments during urologic laparoscopic surgical procedures, gynecologic laparoscopic surgical procedures, general laparoscopic surgical procedures, and thoracoscopic surgical procedures.</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Search results</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>search_page.sort_oldest_label</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Oldest first</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>SHURUI SP Robot</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Surgeon console</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Link label</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Explore more</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Search results</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>search_page.prompt_message</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Type a word or two above to search the site.</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>SHURUI SP Robot</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>System composition</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>System composition</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Search results</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>search_page.empty_message</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Nothing on the site matches “{term}”. Try a different word, or fewer of them.</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>SHURUI SP Robot</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>The SHURUI SP Surgical System</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>line 1</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>System purpose</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Search results</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>search_page.loading_message</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Searching…</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>SHURUI SP Robot</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>The SHURUI SP Surgical System</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>line 2</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>intended use</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1709,336 +2057,417 @@
           <t>Search results</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>search_page.pager_label</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Search result pages</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>title fallback</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Site wide (header, footer, cookie notice)</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>footer.wordmark</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Shurui</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>Search results</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Placeholder text</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Search input</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Site wide (header, footer, cookie notice)</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>footer.wordmark_caption</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>SP Surgical System</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>Search results</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>field label</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Search this site</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Site wide (header, footer, cookie notice)</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>nav_link.label</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>IFU</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>Search results</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>sort name</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Sort by</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>System Principles</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>media_row.body</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>{"type":"doc","content":[{"type":"paragraph","content":[{"text":"The SHURUI inst</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Search results</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>sort oldest label</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Oldest first</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>System Principles</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>statement.headline</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Visualization and control interface</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Search results</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>prompt message</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Type a word or two above to search the site.</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>System Principles</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>statement.watermark</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Visualization &amp;
-control interface</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>Search results</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Empty state message</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Nothing on the site matches “{term}”. Try a different word, or fewer of them.</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Training &amp; Proctoring</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>accordion_item.label</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Vall d’ Hebron University Hospital, Barcelona</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>Search results</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>loading message</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Searching…</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Training &amp; Proctoring</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>accordion_item.body</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>{"type":"doc","content":[{"type":"paragraph","content":[{"text":"Barcelona, Spai</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Search results</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>pager label</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Search result pages</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Training &amp; Proctoring</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>accordion_item.label</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Klinikum Bogenhausen Hospital, Munich</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>Site wide (header, footer, cookie notice)</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>(top of the page)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Shurui</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Training &amp; Proctoring</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>accordion_item.body</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>{"type":"doc","content":[{"type":"paragraph","content":[{"text":"Munich, Germany</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>Site wide (header, footer, cookie notice)</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>(top of the page)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>wordmark caption</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>SP Surgical System</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Training &amp; Proctoring</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>card_band.body</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>{"type":"doc","content":[{"type":"paragraph","content":[{"text":"Access educatio</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>Site wide (header, footer, cookie notice)</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Button or link label</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>IFU</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Training &amp; Proctoring</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>grid_card.body</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Explore procedural demonstrations and system applications.</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>System Principles</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Dual Continuum Mechanism</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Body text</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>The SHURUI instruments are built around a patented Dual Continuum Mechanism composed of multiple flexible elements, including super-elastic nitinol rods. Unlike conventional robotic architectures based on articulated joints, the continuum structure enables smooth, continuous bending along the instrument shaft, providing up to 210° of cumulative bending range through its dual-segment design.
+This continuous deformation capability supports controlled navigation and distal instrument movements within anatomically confined surgical environments.</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Training &amp; Proctoring</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>grid_card.link_label</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Explore our surgical videos</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>System Principles</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Robot overview</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Link label</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Explore more</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Training &amp; Proctoring</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>grid_card.body</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Review scientific evidence and published clinical experience.</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>System Principles</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Visualization and control interface</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Visualization and control interface</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Training &amp; Proctoring</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>grid_card.link_label</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Explore our publications</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>System Principles</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Visualization and control interface</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>watermark</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Visualization &amp;
+control interface</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2046,20 +2475,25 @@
           <t>Training &amp; Proctoring</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>grid_card.body</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Discover real-world clinical experiences and procedural approaches.</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Clinical publications</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Body text</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Review scientific evidence and published clinical experience.</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2067,20 +2501,25 @@
           <t>Training &amp; Proctoring</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>grid_card.link_label</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Explore our surgical booklets</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Clinical publications</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Link label</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Explore our publications</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2088,62 +2527,259 @@
           <t>Training &amp; Proctoring</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>hero_full.body</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Supporting every step of your clinical journey: structured training, practical l</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Educational resources</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Body text</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Access educational materials designed to support procedural knowledge and clinical learning. Discover what's new or see all our resources at the media page.</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>news-events/3cvd-2026</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>article.title</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>3CVD 2026</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>Training &amp; Proctoring</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Reference centers</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Button or link label</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Vall d’ Hebron University Hospital, Barcelona</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>news-events/erus-2026</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>article.title</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>ERUS 2026</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>Training &amp; Proctoring</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Reference centers</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Body text</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Barcelona, Spain</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Training &amp; Proctoring</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Reference centers</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Button or link label</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Klinikum Bogenhausen Hospital, Munich</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Training &amp; Proctoring</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Reference centers</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Body text</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Training &amp; Proctoring</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Surgical booklets</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Body text</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Discover real-world clinical experiences and procedural approaches.</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Training &amp; Proctoring</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Surgical booklets</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Link label</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Explore our surgical booklets</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Training &amp; Proctoring</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Surgical videos</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Body text</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Explore procedural demonstrations and system applications.</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Training &amp; Proctoring</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Surgical videos</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Link label</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Explore our surgical videos</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Training &amp; Proctoring</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Training &amp; proctoring</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Body text</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Supporting every step of your clinical journey: structured training, practical learning, and ongoing clinical support.</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2156,44 +2792,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Where it appears</t>
+          <t>Section on the page</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>What it is</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>English</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
@@ -2202,178 +2844,233 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ifu_item.title</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
           <t>3D Endoscope Reprocessing Instructions</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3D Endoscope Reprocessing Instructions</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ifu_item.placeholder</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+          <t>3D Endoscope Reprocessing Instructions</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Placeholder text</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>(link to PDF see IFU folder)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ifu_item.title</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
           <t>Accessories Reprocessing Instructions</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Accessories Reprocessing Instructions</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ifu_item.title</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
           <t>3D Endoscope Information</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3D Endoscope Information</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ifu_item.title</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
           <t>Energy Instrument Cord Information</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Energy Instrument Cord Information</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ifu_item.title</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
           <t>Instrument Reprocessing Instructions</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Instrument Reprocessing Instructions</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ifu_item.title</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
           <t>Instruments Information</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Instruments Information</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ifu_item.title</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
           <t>Sterile Drape User Manual</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sterile Drape User Manual</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ifu_item.title</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
           <t>Trocar Incision Protector User Manual</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Trocar Incision Protector User Manual</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ifu_item.title</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
           <t>Endoscopic Surgical System Technical Description</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Endoscopic Surgical System Technical Description</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ifu_item.title</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
           <t>Endoscopic Surgical System User Manual</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Endoscopic Surgical System User Manual</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2390,11 +3087,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="96" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="94" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2432,7 +3129,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>About / Contact</t>
+          <t>About and Contact</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -2472,12 +3169,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="56" customWidth="1" min="2" max="2"/>
-    <col width="86" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2488,12 +3186,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Meta title (max 60 chars)</t>
+          <t>Meta title (max 60 characters)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Meta description (max 155 chars)</t>
+          <t>Meta description (max 155 characters)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Currently on the site</t>
         </is>
       </c>
     </row>
@@ -2505,6 +3208,7 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2514,6 +3218,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2523,6 +3228,11 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>How the SHURUI SP Surgical System works: the Dual Continuum Mechanism, push-pull actuation, stereoscopic visualization and the surgeon control interface.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2532,6 +3242,11 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>SHURUI continuum instruments and the flexible 3D endoscope: internal deployment, the Dual Continuum Mechanism and versatile visualization.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2541,6 +3256,11 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>The SHURUI SP Surgical System across urology, gynecology, general and thoracic surgery, including pediatric procedures.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2550,6 +3270,11 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Procedural outcomes, growing clinical experience and published surgical data on the SHURUI SP Surgical System across minimally invasive surgery.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2559,6 +3284,11 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Surgical videos, clinical cases and peer-reviewed publications on the SHURUI SP Surgical System, by specialty.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2568,6 +3298,11 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Structured training, hands-on practice and proctoring support for surgical teams adopting the SHURUI SP Surgical System.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2577,6 +3312,11 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Surgerii Robotics is a medical technology company advancing single-port robotic surgery. Its founder, patents, offices and quality framework.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2586,15 +3326,21 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Connect with the SHURUI team to learn more about the SHURUI SP Surgical System, request a demonstration or find a clinical center near you.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>News Events</t>
+          <t>News &amp; events</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2604,15 +3350,25 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Search the SHURUI site.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Clinical Centers</t>
+          <t>Clinical centers</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>The hospitals and medical centres working with the SHURUI SP Surgical System, by country.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2622,33 +3378,582 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Instructions for use, reprocessing instructions and user manuals for the SHURUI Endoscopic Surgical System (SR-ENS-600) and its accessories.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Privacy Policy</t>
+          <t>Privacy policy</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>How Surgerii Robotics (Netherlands) B.V. processes personal data collected through this website, and the rights you have under the GDPR.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Legal Notice</t>
+          <t>Legal notice</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Who operates this website, its role as EU Authorised Representative under the MDR, and the disclaimer and copyright terms that apply to its content.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cookie Policy</t>
+          <t>Cookie policy</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Which cookies and similar technologies this website uses, on what legal basis, and how to change or withdraw your consent.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Why it is not listed</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>About</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>About</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>About</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>About</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>488+</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Clinical Applications</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1,800+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Clinical Applications</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>101+</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Clinical Applications</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>110+</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Clinical Applications</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Clinical Evidence</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1,800+</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Clinical Evidence</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>101+</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Clinical Evidence</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>110+</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Clinical Evidence</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Clinical Library</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Clinical Library placeholder card</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Header 01</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Clinical Library</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Clinical Library placeholder card</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Lorem ipsum dolor sit amet, consectetur adipiscing elit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Clinical centers</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>City name</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Clinical centers</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>City name</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Clinical centers</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>City name</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Chongqing</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Clinical centers</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>City name</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Clinical centers</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>City name</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Nanjing</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Clinical centers</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>City name</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Clinical centers</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>City name</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Xiaogan</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Clinical centers</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>City name</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Xi’an</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1,800+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>101+</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>110+</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1,800+</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>101+</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>110+</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
